--- a/output/pdf_financials_xlsx/NCAU.xlsx
+++ b/output/pdf_financials_xlsx/NCAU.xlsx
@@ -1201,31 +1201,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.054942</v>
+        <v>-0.054942</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.451043</v>
+        <v>-0.451043</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.271749</v>
+        <v>-0.271749</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.612548</v>
+        <v>-0.612548</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.157923</v>
+        <v>-0.157923</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.625494</v>
+        <v>-0.625494</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.526843</v>
+        <v>-0.526843</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.008307</v>
+        <v>-1.008307</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.516962</v>
+        <v>-0.516962</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4.020725</v>
+        <v>-4.020725</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.625137</v>
+        <v>-2.625137</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>2.423771</v>
@@ -1473,31 +1473,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.054942</v>
+        <v>-0.054942</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.451043</v>
+        <v>-0.451043</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.271749</v>
+        <v>-0.271749</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.612548</v>
+        <v>-0.612548</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.157923</v>
+        <v>-0.157923</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.625494</v>
+        <v>-0.625494</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.526843</v>
+        <v>-0.526843</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.008307</v>
+        <v>-1.008307</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.516962</v>
+        <v>-0.516962</v>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
@@ -1505,19 +1505,19 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>4.020725</v>
+        <v>-4.020725</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.625137</v>
+        <v>-2.625137</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>3.365909</v>
+        <v>-3.365909</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5.272345</v>
+        <v>-5.272345</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.772927</v>
+        <v>-1.772927</v>
       </c>
     </row>
     <row r="21">
@@ -1635,49 +1635,49 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.054942</v>
+        <v>-0.054942</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.451043</v>
+        <v>-0.451043</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.271749</v>
+        <v>-0.271749</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.612548</v>
+        <v>-0.612548</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.157923</v>
+        <v>-0.157923</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.625494</v>
+        <v>-0.625494</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.526843</v>
+        <v>-0.526843</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.008307</v>
+        <v>-1.008307</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.516962</v>
+        <v>-0.516962</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.270655</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>4.020725</v>
+        <v>-4.020725</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.625137</v>
+        <v>-2.625137</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>3.365909</v>
+        <v>-3.365909</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>5.272345</v>
+        <v>-5.272345</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.772927</v>
+        <v>-1.772927</v>
       </c>
     </row>
     <row r="24">
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>22.55215</v>
+        <v>-22.55215</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5.568618</v>
+        <v>-5.568618</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>7.89615</v>
+        <v>-7.89615</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>50.41535</v>
+        <v>-50.41535</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -1837,16 +1837,16 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>100.518125</v>
+        <v>-100.518125</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>131.25685</v>
+        <v>-131.25685</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>168.29545</v>
+        <v>-168.29545</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>175.744833</v>
+        <v>-175.744833</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -1861,31 +1861,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.054942</v>
+        <v>-0.054942</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.451043</v>
+        <v>-0.451043</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.271749</v>
+        <v>-0.271749</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.612548</v>
+        <v>-0.612548</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.157923</v>
+        <v>-0.157923</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.625494</v>
+        <v>-0.625494</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.526843</v>
+        <v>-0.526843</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.008307</v>
+        <v>-1.008307</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.516962</v>
+        <v>-0.516962</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>4.020725</v>
+        <v>-4.020725</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.625137</v>
+        <v>-2.625137</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>2.423771</v>
@@ -1969,31 +1969,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.054942</v>
+        <v>-0.054942</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.451043</v>
+        <v>-0.451043</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.271749</v>
+        <v>-0.271749</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.612548</v>
+        <v>-0.612548</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.157923</v>
+        <v>-0.157923</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.625494</v>
+        <v>-0.625494</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.526843</v>
+        <v>-0.526843</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.008307</v>
+        <v>-1.008307</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.516962</v>
+        <v>-0.516962</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>4.020725</v>
+        <v>-4.020725</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.625137</v>
+        <v>-2.625137</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>2.423771</v>
@@ -2105,31 +2105,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>38.8707514034948</v>
@@ -5343,46 +5343,46 @@
         <v>0.010576</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.470944</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.510915</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.510915</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.568491</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.925182</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.294765</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.001596</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.198502</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.198502</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.396039</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.851306</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.851306</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.132352</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>9.029341000000001</v>
       </c>
     </row>
     <row r="93">
@@ -8694,7 +8694,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -8761,7 +8765,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11878,7 +11886,11 @@
           <t>Share-based payments reserve 4,135,988</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -11967,7 +11979,11 @@
           <t>Warrants reserve 2,996,364</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -23748,7 +23764,11 @@
           <t>Share-based payments reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -23837,7 +23857,11 @@
           <t>Warrants reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -25291,7 +25315,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -25380,7 +25408,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -28102,7 +28134,11 @@
           <t>Warrants reserve 306,929 10,576</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -37621,19 +37657,19 @@
         </is>
       </c>
       <c r="O338" s="5" t="n">
-        <v>4.020725</v>
+        <v>-4.020725</v>
       </c>
       <c r="P338" s="5" t="n">
-        <v>2.625137</v>
+        <v>-2.625137</v>
       </c>
       <c r="Q338" s="5" t="n">
-        <v>3.365909</v>
+        <v>-3.365909</v>
       </c>
       <c r="R338" s="5" t="n">
-        <v>5.272345</v>
+        <v>-5.272345</v>
       </c>
       <c r="S338" s="5" t="n">
-        <v>1.772927</v>
+        <v>-1.772927</v>
       </c>
     </row>
     <row r="339">
@@ -38222,16 +38258,16 @@
         </is>
       </c>
       <c r="O345" s="5" t="n">
-        <v>3.872862</v>
+        <v>-3.872862</v>
       </c>
       <c r="P345" s="5" t="n">
-        <v>1.223155</v>
+        <v>-1.223155</v>
       </c>
       <c r="Q345" s="5" t="n">
-        <v>4.20835</v>
+        <v>-4.20835</v>
       </c>
       <c r="R345" s="5" t="n">
-        <v>1.860531</v>
+        <v>-1.860531</v>
       </c>
       <c r="S345" t="inlineStr">
         <is>
@@ -38403,10 +38439,10 @@
         </is>
       </c>
       <c r="P347" s="5" t="n">
-        <v>2.625137</v>
+        <v>-2.625137</v>
       </c>
       <c r="Q347" s="5" t="n">
-        <v>2.423771</v>
+        <v>-2.423771</v>
       </c>
       <c r="R347" t="inlineStr">
         <is>
@@ -38496,10 +38532,10 @@
         </is>
       </c>
       <c r="P348" s="5" t="n">
-        <v>1.223155</v>
+        <v>-1.223155</v>
       </c>
       <c r="Q348" s="5" t="n">
-        <v>3.340103</v>
+        <v>-3.340103</v>
       </c>
       <c r="R348" t="inlineStr">
         <is>
@@ -38875,22 +38911,22 @@
         </is>
       </c>
       <c r="H353" s="5" t="n">
-        <v>0.612548</v>
+        <v>-0.612548</v>
       </c>
       <c r="I353" s="5" t="n">
-        <v>0.157923</v>
+        <v>-0.157923</v>
       </c>
       <c r="J353" s="5" t="n">
-        <v>0.625494</v>
+        <v>-0.625494</v>
       </c>
       <c r="K353" s="5" t="n">
-        <v>0.526843</v>
+        <v>-0.526843</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>1.008307</v>
+        <v>-1.008307</v>
       </c>
       <c r="M353" s="5" t="n">
-        <v>0.516962</v>
+        <v>-0.516962</v>
       </c>
       <c r="N353" t="inlineStr">
         <is>
@@ -39400,10 +39436,10 @@
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>0.879452</v>
+        <v>-0.879452</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>1.748367</v>
+        <v>-1.748367</v>
       </c>
       <c r="M359" t="inlineStr">
         <is>
@@ -40725,16 +40761,16 @@
         </is>
       </c>
       <c r="E374" s="5" t="n">
-        <v>0.054942</v>
+        <v>-0.054942</v>
       </c>
       <c r="F374" s="5" t="n">
-        <v>0.451043</v>
+        <v>-0.451043</v>
       </c>
       <c r="G374" s="5" t="n">
-        <v>0.271749</v>
+        <v>-0.271749</v>
       </c>
       <c r="H374" s="5" t="n">
-        <v>0.612548</v>
+        <v>-0.612548</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NCAU.xlsx
+++ b/output/pdf_financials_xlsx/NCAU.xlsx
@@ -988,28 +988,28 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00266</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003197</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000728</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000264</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005979</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.020268</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011953</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012522</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025008</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.037709</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.181281</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09063400000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.14842</v>
       </c>
     </row>
     <row r="13">
@@ -1864,28 +1864,28 @@
         <v>-0.054942</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.451043</v>
+        <v>-0.448383</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.271749</v>
+        <v>-0.268552</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.612548</v>
+        <v>-0.61182</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.157923</v>
+        <v>-0.157659</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.625494</v>
+        <v>-0.619515</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.526843</v>
+        <v>-0.506575</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.008307</v>
+        <v>-0.996354</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.516962</v>
+        <v>-0.50444</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -1893,19 +1893,19 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.020725</v>
+        <v>-3.995717</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.625137</v>
+        <v>-2.587428</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.423771</v>
+        <v>2.605052</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.064712</v>
+        <v>4.155346</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>5.33359</v>
+        <v>5.48201</v>
       </c>
     </row>
     <row r="28">
@@ -1972,28 +1972,28 @@
         <v>-0.054942</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.451043</v>
+        <v>-0.448383</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.271749</v>
+        <v>-0.268552</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.612548</v>
+        <v>-0.61182</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.157923</v>
+        <v>-0.157659</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.625494</v>
+        <v>-0.619515</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.526843</v>
+        <v>-0.506575</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.008307</v>
+        <v>-0.996354</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.516962</v>
+        <v>-0.50444</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2001,19 +2001,19 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.020725</v>
+        <v>-3.995717</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.625137</v>
+        <v>-2.587428</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.423771</v>
+        <v>2.605052</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.064712</v>
+        <v>4.155346</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.33359</v>
+        <v>5.48201</v>
       </c>
     </row>
     <row r="30">
@@ -2251,31 +2251,31 @@
         <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.779407</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.26554</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.09080199999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.570474</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.036576</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.025899</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.901456</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.379657</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.092386</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.775007</v>
@@ -2355,31 +2355,31 @@
         <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.779407</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.26554</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.09080199999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.570474</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.455</v>
+        <v>1.491576</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.106915</v>
+        <v>1.132814</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.038569</v>
+        <v>1.940025</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.721436</v>
+        <v>1.101093</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.432</v>
+        <v>0.524386</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>5.525007</v>
@@ -2979,31 +2979,31 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.779407</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.26554</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.09080199999999999</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.598076</v>
+        <v>0.027602</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.080183</v>
+        <v>0.043607</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.050248</v>
+        <v>0.024349</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.926934</v>
+        <v>0.025478</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.406622</v>
+        <v>0.026965</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.149554</v>
+        <v>0.057168</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.250532</v>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -37348,7 +37348,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -41671,7 +41671,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">

--- a/output/pdf_financials_xlsx/NCAU.xlsx
+++ b/output/pdf_financials_xlsx/NCAU.xlsx
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>0.08914900000000001</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>0.08914900000000001</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>0.083902</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>0</v>
@@ -3492,13 +3492,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>0.013113</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>0.013358</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>0.013744</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>0</v>
@@ -4030,13 +4030,13 @@
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.062942</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.561953</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.06426900000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4082,13 +4082,13 @@
         <v>0.380517</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.380517</v>
+        <v>0.443459</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>1.852738</v>
+        <v>2.414691</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>2.337942</v>
+        <v>2.402211</v>
       </c>
     </row>
     <row r="69">
@@ -4446,7 +4446,7 @@
         <v>3.569836</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>2.552069</v>
+        <v>2.489127</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S386"/>
+  <dimension ref="A1:S405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30650,7 +30650,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -31422,7 +31426,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -31999,7 +32007,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -36162,20 +36174,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Incorporation to</t>
+        </is>
+      </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>December 31, 2025 December</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E320" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -36237,34 +36251,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R320" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="S320" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Share-based compensation $</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the period $</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="n">
+        <v>-0.054942</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -36311,47 +36331,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O321" s="5" t="n">
-        <v>1.460866</v>
-      </c>
-      <c r="P321" s="5" t="n">
-        <v>0.867735</v>
-      </c>
-      <c r="Q321" s="5" t="n">
-        <v>0.377058</v>
-      </c>
-      <c r="R321" s="5" t="n">
-        <v>0.371275</v>
-      </c>
-      <c r="S321" s="5" t="n">
-        <v>1.567186</v>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Net changes in non-cash working capital components</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Management fees</t>
+          <t>Change in operating accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="n">
+        <v>0.015299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -36363,66 +36391,86 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H322" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I322" s="5" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="J322" s="5" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="K322" s="5" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="L322" s="5" t="n">
-        <v>0.071494</v>
-      </c>
-      <c r="M322" s="5" t="n">
-        <v>0.178445</v>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N322" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O322" s="5" t="n">
-        <v>1.311416</v>
-      </c>
-      <c r="P322" s="5" t="n">
-        <v>0.767673</v>
-      </c>
-      <c r="Q322" s="5" t="n">
-        <v>1.214913</v>
-      </c>
-      <c r="R322" s="5" t="n">
-        <v>2.864884</v>
-      </c>
-      <c r="S322" s="5" t="n">
-        <v>2.130908</v>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Net changes in non-cash working capital components</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Shareholder relations, marketing and conferences</t>
+          <t>Net changes in non-cash working capital components total</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E323" s="5" t="n">
+        <v>-0.039643</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -36469,43 +36517,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O323" s="5" t="n">
-        <v>0.53659</v>
-      </c>
-      <c r="P323" s="5" t="n">
-        <v>0.408884</v>
-      </c>
-      <c r="Q323" s="5" t="n">
-        <v>0.364481</v>
-      </c>
-      <c r="R323" s="5" t="n">
-        <v>0.403512</v>
-      </c>
-      <c r="S323" s="5" t="n">
-        <v>0.532176</v>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Accounting and audit fees</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds on share issuance (Note 3)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="n">
+        <v>0.47</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -36552,47 +36612,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O324" s="5" t="n">
-        <v>0.073354</v>
-      </c>
-      <c r="P324" s="5" t="n">
-        <v>0.096069</v>
-      </c>
-      <c r="Q324" s="5" t="n">
-        <v>0.065914</v>
-      </c>
-      <c r="R324" s="5" t="n">
-        <v>0.045029</v>
-      </c>
-      <c r="S324" s="5" t="n">
-        <v>0.09803000000000001</v>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="n">
+        <v>-0.106659</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -36629,124 +36697,156 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M325" s="5" t="n">
-        <v>0.019837</v>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O325" s="5" t="n">
-        <v>0.050543</v>
-      </c>
-      <c r="P325" s="5" t="n">
-        <v>0.123318</v>
-      </c>
-      <c r="Q325" s="5" t="n">
-        <v>0.08641799999999999</v>
-      </c>
-      <c r="R325" s="5" t="n">
-        <v>0.170012</v>
-      </c>
-      <c r="S325" s="5" t="n">
-        <v>0.225351</v>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>FINANCING total</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" s="5" t="n">
-        <v>0.000956</v>
-      </c>
-      <c r="F326" s="5" t="n">
-        <v>0.000177</v>
-      </c>
-      <c r="G326" s="5" t="n">
-        <v>0.000164</v>
-      </c>
-      <c r="H326" s="5" t="n">
-        <v>0.000564</v>
-      </c>
-      <c r="I326" s="5" t="n">
-        <v>0.006068</v>
-      </c>
-      <c r="J326" s="5" t="n">
-        <v>0.06972200000000001</v>
-      </c>
-      <c r="K326" s="5" t="n">
-        <v>0.024106</v>
-      </c>
-      <c r="L326" s="5" t="n">
-        <v>0.035567</v>
-      </c>
-      <c r="M326" s="5" t="n">
-        <v>0.031637</v>
+        <v>0.363341</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N326" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O326" s="5" t="n">
-        <v>0.099151</v>
-      </c>
-      <c r="P326" s="5" t="n">
-        <v>0.100624</v>
-      </c>
-      <c r="Q326" s="5" t="n">
-        <v>0.087063</v>
-      </c>
-      <c r="R326" s="5" t="n">
-        <v>0.094467</v>
-      </c>
-      <c r="S326" s="5" t="n">
-        <v>0.107621</v>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Net increase in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="n">
+        <v>0.323698</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -36763,61 +36863,81 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I327" s="5" t="n">
-        <v>0.000958</v>
-      </c>
-      <c r="J327" s="5" t="n">
-        <v>0.024512</v>
-      </c>
-      <c r="K327" s="5" t="n">
-        <v>0.026628</v>
-      </c>
-      <c r="L327" s="5" t="n">
-        <v>0.025984</v>
-      </c>
-      <c r="M327" s="5" t="n">
-        <v>0.027961</v>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N327" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O327" s="5" t="n">
-        <v>0.056147</v>
-      </c>
-      <c r="P327" s="5" t="n">
-        <v>0.059164</v>
-      </c>
-      <c r="Q327" s="5" t="n">
-        <v>0.063219</v>
-      </c>
-      <c r="R327" s="5" t="n">
-        <v>0.062982</v>
-      </c>
-      <c r="S327" s="5" t="n">
-        <v>0.063732</v>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Cash and cash equivalents – beginning of year</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -36825,72 +36945,100 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F328" s="5" t="n">
-        <v>0.09585100000000001</v>
-      </c>
-      <c r="G328" s="5" t="n">
-        <v>0.007719</v>
-      </c>
-      <c r="H328" s="5" t="n">
-        <v>0.011149</v>
-      </c>
-      <c r="I328" s="5" t="n">
-        <v>0.040342</v>
-      </c>
-      <c r="J328" s="5" t="n">
-        <v>0.014789</v>
-      </c>
-      <c r="K328" s="5" t="n">
-        <v>0.00443</v>
-      </c>
-      <c r="L328" s="5" t="n">
-        <v>0.006307</v>
-      </c>
-      <c r="M328" s="5" t="n">
-        <v>0.005193</v>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N328" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O328" s="5" t="n">
-        <v>0.08717</v>
-      </c>
-      <c r="P328" s="5" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="Q328" s="5" t="n">
-        <v>0.027214</v>
-      </c>
-      <c r="R328" s="5" t="n">
-        <v>0.09654500000000001</v>
-      </c>
-      <c r="S328" s="5" t="n">
-        <v>0.07793700000000001</v>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Salaries</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents – end of year $</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="n">
+        <v>0.323698</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -36957,79 +37105,105 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S329" s="5" t="n">
-        <v>0.019375</v>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash financing activities</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Transfer agent and regulatory fees</t>
+          <t>Warrants issued for share issue costs $</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F330" s="5" t="n">
-        <v>0.085439</v>
-      </c>
-      <c r="G330" s="5" t="n">
-        <v>0.016608</v>
-      </c>
-      <c r="H330" s="5" t="n">
-        <v>0.015817</v>
-      </c>
-      <c r="I330" s="5" t="n">
-        <v>0.030047</v>
-      </c>
-      <c r="J330" s="5" t="n">
-        <v>0.018242</v>
-      </c>
-      <c r="K330" s="5" t="n">
-        <v>0.014585</v>
-      </c>
-      <c r="L330" s="5" t="n">
-        <v>0.014428</v>
-      </c>
-      <c r="M330" s="5" t="n">
-        <v>0.013743</v>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="n">
+        <v>0.010576</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O330" s="5" t="n">
-        <v>0.071379</v>
-      </c>
-      <c r="P330" s="5" t="n">
-        <v>0.034781</v>
-      </c>
-      <c r="Q330" s="5" t="n">
-        <v>0.108345</v>
-      </c>
-      <c r="R330" s="5" t="n">
-        <v>0.096454</v>
-      </c>
-      <c r="S330" s="5" t="n">
-        <v>0.141805</v>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="331">
@@ -37038,14 +37212,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Consultants</t>
+          <t>December 31, 2025 December</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -37064,45 +37234,61 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H331" s="5" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="I331" s="5" t="n">
-        <v>0.001689</v>
-      </c>
-      <c r="J331" s="5" t="n">
-        <v>0.063392</v>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L331" s="5" t="n">
-        <v>0.045001</v>
-      </c>
-      <c r="M331" s="5" t="n">
-        <v>0.018354</v>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N331" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O331" s="5" t="n">
-        <v>0.093637</v>
-      </c>
-      <c r="P331" s="5" t="n">
-        <v>0.08253199999999999</v>
-      </c>
-      <c r="Q331" s="5" t="n">
-        <v>0.016432</v>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R331" s="5" t="n">
-        <v>0.0658</v>
+        <v>0.002024</v>
       </c>
       <c r="S331" s="5" t="n">
-        <v>0.06</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="332">
@@ -37118,14 +37304,10 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Share-based compensation $</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -37146,20 +37328,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I332" s="5" t="n">
-        <v>0.000614</v>
-      </c>
-      <c r="J332" s="5" t="n">
-        <v>0.002254</v>
-      </c>
-      <c r="K332" s="5" t="n">
-        <v>0.00168</v>
-      </c>
-      <c r="L332" s="5" t="n">
-        <v>0.000245</v>
-      </c>
-      <c r="M332" s="5" t="n">
-        <v>0.000386</v>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N332" t="inlineStr">
         <is>
@@ -37167,19 +37359,19 @@
         </is>
       </c>
       <c r="O332" s="5" t="n">
-        <v>0.006407</v>
+        <v>1.460866</v>
       </c>
       <c r="P332" s="5" t="n">
-        <v>0.009346</v>
+        <v>0.867735</v>
       </c>
       <c r="Q332" s="5" t="n">
-        <v>0.011292</v>
+        <v>0.377058</v>
       </c>
       <c r="R332" s="5" t="n">
-        <v>0.016327</v>
+        <v>0.371275</v>
       </c>
       <c r="S332" s="5" t="n">
-        <v>0.039975</v>
+        <v>1.567186</v>
       </c>
     </row>
     <row r="333">
@@ -37195,12 +37387,12 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
+          <t>Management fees</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -37218,27 +37410,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H333" s="5" t="n">
+        <v>0.05</v>
       </c>
       <c r="I333" s="5" t="n">
-        <v>-0.02838</v>
+        <v>0.0025</v>
       </c>
       <c r="J333" s="5" t="n">
-        <v>0.011647</v>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.102</v>
+      </c>
+      <c r="K333" s="5" t="n">
+        <v>0.0504</v>
       </c>
       <c r="L333" s="5" t="n">
-        <v>0.046182</v>
+        <v>0.071494</v>
       </c>
       <c r="M333" s="5" t="n">
-        <v>-0.021878</v>
+        <v>0.178445</v>
       </c>
       <c r="N333" t="inlineStr">
         <is>
@@ -37246,19 +37434,19 @@
         </is>
       </c>
       <c r="O333" s="5" t="n">
-        <v>0.199073</v>
+        <v>1.311416</v>
       </c>
       <c r="P333" s="5" t="n">
-        <v>0.08412</v>
+        <v>0.767673</v>
       </c>
       <c r="Q333" s="5" t="n">
-        <v>0.182703</v>
+        <v>1.214913</v>
       </c>
       <c r="R333" s="5" t="n">
-        <v>-0.131941</v>
+        <v>2.864884</v>
       </c>
       <c r="S333" s="5" t="n">
-        <v>0.417914</v>
+        <v>2.130908</v>
       </c>
     </row>
     <row r="334">
@@ -37274,40 +37462,54 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E334" s="5" t="n">
-        <v>0.054942</v>
-      </c>
-      <c r="F334" s="5" t="n">
-        <v>0.453703</v>
-      </c>
-      <c r="G334" s="5" t="n">
-        <v>0.274946</v>
-      </c>
-      <c r="H334" s="5" t="n">
-        <v>0.613276</v>
-      </c>
-      <c r="I334" s="5" t="n">
-        <v>0.158188</v>
-      </c>
-      <c r="J334" s="5" t="n">
-        <v>0.631473</v>
-      </c>
-      <c r="K334" s="5" t="n">
-        <v>0.547111</v>
-      </c>
-      <c r="L334" s="5" t="n">
-        <v>1.020259</v>
-      </c>
-      <c r="M334" s="5" t="n">
-        <v>0.529484</v>
+          <t>Shareholder relations, marketing and conferences</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N334" t="inlineStr">
         <is>
@@ -37315,19 +37517,19 @@
         </is>
       </c>
       <c r="O334" s="5" t="n">
-        <v>4.045733</v>
+        <v>0.53659</v>
       </c>
       <c r="P334" s="5" t="n">
-        <v>2.662846</v>
+        <v>0.408884</v>
       </c>
       <c r="Q334" s="5" t="n">
-        <v>2.605052</v>
+        <v>0.364481</v>
       </c>
       <c r="R334" s="5" t="n">
-        <v>4.155346</v>
+        <v>0.403512</v>
       </c>
       <c r="S334" s="5" t="n">
-        <v>5.48201</v>
+        <v>0.532176</v>
       </c>
     </row>
     <row r="335">
@@ -37338,47 +37540,59 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Accounting and audit fees</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F335" s="5" t="n">
-        <v>-0.00266</v>
-      </c>
-      <c r="G335" s="5" t="n">
-        <v>-0.003197</v>
-      </c>
-      <c r="H335" s="5" t="n">
-        <v>-0.000728</v>
-      </c>
-      <c r="I335" s="5" t="n">
-        <v>-0.000264</v>
-      </c>
-      <c r="J335" s="5" t="n">
-        <v>-0.005979</v>
-      </c>
-      <c r="K335" s="5" t="n">
-        <v>-0.020268</v>
-      </c>
-      <c r="L335" s="5" t="n">
-        <v>-0.011953</v>
-      </c>
-      <c r="M335" s="5" t="n">
-        <v>-0.012522</v>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
@@ -37386,19 +37600,19 @@
         </is>
       </c>
       <c r="O335" s="5" t="n">
-        <v>-0.025008</v>
+        <v>0.073354</v>
       </c>
       <c r="P335" s="5" t="n">
-        <v>-0.037709</v>
+        <v>0.096069</v>
       </c>
       <c r="Q335" s="5" t="n">
-        <v>-0.181281</v>
+        <v>0.065914</v>
       </c>
       <c r="R335" s="5" t="n">
-        <v>-0.09063400000000001</v>
+        <v>0.045029</v>
       </c>
       <c r="S335" s="5" t="n">
-        <v>-0.14842</v>
+        <v>0.09803000000000001</v>
       </c>
     </row>
     <row r="336">
@@ -37409,17 +37623,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -37462,34 +37676,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M336" s="5" t="n">
+        <v>0.019837</v>
       </c>
       <c r="N336" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O336" s="5" t="n">
+        <v>0.050543</v>
+      </c>
+      <c r="P336" s="5" t="n">
+        <v>0.123318</v>
       </c>
       <c r="Q336" s="5" t="n">
-        <v>2.423771</v>
+        <v>0.08641799999999999</v>
       </c>
       <c r="R336" s="5" t="n">
-        <v>4.064712</v>
+        <v>0.170012</v>
       </c>
       <c r="S336" s="5" t="n">
-        <v>5.33359</v>
+        <v>0.225351</v>
       </c>
     </row>
     <row r="337">
@@ -37500,89 +37708,65 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery)</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="n">
+        <v>0.000956</v>
+      </c>
+      <c r="F337" s="5" t="n">
+        <v>0.000177</v>
+      </c>
+      <c r="G337" s="5" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="H337" s="5" t="n">
+        <v>0.000564</v>
+      </c>
+      <c r="I337" s="5" t="n">
+        <v>0.006068</v>
+      </c>
+      <c r="J337" s="5" t="n">
+        <v>0.06972200000000001</v>
+      </c>
+      <c r="K337" s="5" t="n">
+        <v>0.024106</v>
+      </c>
+      <c r="L337" s="5" t="n">
+        <v>0.035567</v>
+      </c>
+      <c r="M337" s="5" t="n">
+        <v>0.031637</v>
       </c>
       <c r="N337" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O337" s="5" t="n">
+        <v>0.099151</v>
+      </c>
+      <c r="P337" s="5" t="n">
+        <v>0.100624</v>
+      </c>
+      <c r="Q337" s="5" t="n">
+        <v>0.087063</v>
       </c>
       <c r="R337" s="5" t="n">
-        <v>1.207633</v>
+        <v>0.094467</v>
       </c>
       <c r="S337" s="5" t="n">
-        <v>-3.560663</v>
+        <v>0.107621</v>
       </c>
     </row>
     <row r="338">
@@ -37593,17 +37777,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -37626,30 +37810,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I338" s="5" t="n">
+        <v>0.000958</v>
+      </c>
+      <c r="J338" s="5" t="n">
+        <v>0.024512</v>
+      </c>
+      <c r="K338" s="5" t="n">
+        <v>0.026628</v>
+      </c>
+      <c r="L338" s="5" t="n">
+        <v>0.025984</v>
+      </c>
+      <c r="M338" s="5" t="n">
+        <v>0.027961</v>
       </c>
       <c r="N338" t="inlineStr">
         <is>
@@ -37657,19 +37831,19 @@
         </is>
       </c>
       <c r="O338" s="5" t="n">
-        <v>-4.020725</v>
+        <v>0.056147</v>
       </c>
       <c r="P338" s="5" t="n">
-        <v>-2.625137</v>
+        <v>0.059164</v>
       </c>
       <c r="Q338" s="5" t="n">
-        <v>-3.365909</v>
+        <v>0.063219</v>
       </c>
       <c r="R338" s="5" t="n">
-        <v>-5.272345</v>
+        <v>0.062982</v>
       </c>
       <c r="S338" s="5" t="n">
-        <v>-1.772927</v>
+        <v>0.063732</v>
       </c>
     </row>
     <row r="339">
@@ -37680,59 +37854,47 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Foreign currency translation</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F339" s="5" t="n">
+        <v>0.09585100000000001</v>
+      </c>
+      <c r="G339" s="5" t="n">
+        <v>0.007719</v>
+      </c>
+      <c r="H339" s="5" t="n">
+        <v>0.011149</v>
+      </c>
+      <c r="I339" s="5" t="n">
+        <v>0.040342</v>
+      </c>
+      <c r="J339" s="5" t="n">
+        <v>0.014789</v>
+      </c>
+      <c r="K339" s="5" t="n">
+        <v>0.00443</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>0.006307</v>
+      </c>
+      <c r="M339" s="5" t="n">
+        <v>0.005193</v>
       </c>
       <c r="N339" t="inlineStr">
         <is>
@@ -37740,19 +37902,19 @@
         </is>
       </c>
       <c r="O339" s="5" t="n">
-        <v>-0.147863</v>
+        <v>0.08717</v>
       </c>
       <c r="P339" s="5" t="n">
-        <v>-1.401982</v>
+        <v>0.0286</v>
       </c>
       <c r="Q339" s="5" t="n">
-        <v>0.842441</v>
+        <v>0.027214</v>
       </c>
       <c r="R339" s="5" t="n">
-        <v>-3.411814</v>
+        <v>0.09654500000000001</v>
       </c>
       <c r="S339" s="5" t="n">
-        <v>2.580225</v>
+        <v>0.07793700000000001</v>
       </c>
     </row>
     <row r="340">
@@ -37763,12 +37925,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Comprehensive loss (income) for the year</t>
+          <t>Salaries</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -37837,11 +37999,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R340" s="5" t="n">
-        <v>1.860531</v>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S340" s="5" t="n">
-        <v>4.353152</v>
+        <v>0.019375</v>
       </c>
     </row>
     <row r="341">
@@ -37852,57 +38016,47 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>Transfer agent and regulatory fees</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E341" s="5" t="n">
-        <v>1e-08</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F341" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.085439</v>
       </c>
       <c r="G341" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016608</v>
+      </c>
+      <c r="H341" s="5" t="n">
+        <v>0.015817</v>
+      </c>
+      <c r="I341" s="5" t="n">
+        <v>0.030047</v>
+      </c>
+      <c r="J341" s="5" t="n">
+        <v>0.018242</v>
+      </c>
+      <c r="K341" s="5" t="n">
+        <v>0.014585</v>
+      </c>
+      <c r="L341" s="5" t="n">
+        <v>0.014428</v>
+      </c>
+      <c r="M341" s="5" t="n">
+        <v>0.013743</v>
       </c>
       <c r="N341" t="inlineStr">
         <is>
@@ -37910,19 +38064,19 @@
         </is>
       </c>
       <c r="O341" s="5" t="n">
-        <v>4e-08</v>
+        <v>0.071379</v>
       </c>
       <c r="P341" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.034781</v>
       </c>
       <c r="Q341" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.108345</v>
       </c>
       <c r="R341" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.096454</v>
       </c>
       <c r="S341" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.141805</v>
       </c>
     </row>
     <row r="342">
@@ -37933,12 +38087,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Consultants</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -37957,35 +38111,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H342" s="5" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I342" s="5" t="n">
+        <v>0.001689</v>
+      </c>
+      <c r="J342" s="5" t="n">
+        <v>0.063392</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L342" s="5" t="n">
+        <v>0.045001</v>
+      </c>
+      <c r="M342" s="5" t="n">
+        <v>0.018354</v>
       </c>
       <c r="N342" t="inlineStr">
         <is>
@@ -37993,19 +38137,19 @@
         </is>
       </c>
       <c r="O342" s="5" t="n">
-        <v>107.819163</v>
+        <v>0.093637</v>
       </c>
       <c r="P342" s="5" t="n">
-        <v>129.079858</v>
+        <v>0.08253199999999999</v>
       </c>
       <c r="Q342" s="5" t="n">
-        <v>155.412367</v>
+        <v>0.016432</v>
       </c>
       <c r="R342" s="5" t="n">
-        <v>187.635124</v>
+        <v>0.0658</v>
       </c>
       <c r="S342" s="5" t="n">
-        <v>248.845949</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="343">
@@ -38014,13 +38158,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>December 31, 2024 December</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -38041,56 +38193,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I343" s="5" t="n">
+        <v>0.000614</v>
+      </c>
+      <c r="J343" s="5" t="n">
+        <v>0.002254</v>
+      </c>
+      <c r="K343" s="5" t="n">
+        <v>0.00168</v>
+      </c>
+      <c r="L343" s="5" t="n">
+        <v>0.000245</v>
+      </c>
+      <c r="M343" s="5" t="n">
+        <v>0.000386</v>
       </c>
       <c r="N343" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O343" s="5" t="n">
+        <v>0.006407</v>
+      </c>
+      <c r="P343" s="5" t="n">
+        <v>0.009346</v>
       </c>
       <c r="Q343" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.011292</v>
       </c>
       <c r="R343" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="S343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016327</v>
+      </c>
+      <c r="S343" s="5" t="n">
+        <v>0.039975</v>
       </c>
     </row>
     <row r="344">
@@ -38101,17 +38237,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Deferred income tax expense</t>
+          <t>Foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -38134,56 +38270,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I344" s="5" t="n">
+        <v>-0.02838</v>
+      </c>
+      <c r="J344" s="5" t="n">
+        <v>0.011647</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L344" s="5" t="n">
+        <v>0.046182</v>
+      </c>
+      <c r="M344" s="5" t="n">
+        <v>-0.021878</v>
       </c>
       <c r="N344" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O344" s="5" t="n">
+        <v>0.199073</v>
+      </c>
+      <c r="P344" s="5" t="n">
+        <v>0.08412</v>
       </c>
       <c r="Q344" s="5" t="n">
-        <v>0.942138</v>
+        <v>0.182703</v>
       </c>
       <c r="R344" s="5" t="n">
-        <v>1.207633</v>
-      </c>
-      <c r="S344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.131941</v>
+      </c>
+      <c r="S344" s="5" t="n">
+        <v>0.417914</v>
       </c>
     </row>
     <row r="345">
@@ -38194,63 +38316,45 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
+          <t>EXPENSES total</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="n">
+        <v>0.054942</v>
+      </c>
+      <c r="F345" s="5" t="n">
+        <v>0.453703</v>
+      </c>
+      <c r="G345" s="5" t="n">
+        <v>0.274946</v>
+      </c>
+      <c r="H345" s="5" t="n">
+        <v>0.613276</v>
+      </c>
+      <c r="I345" s="5" t="n">
+        <v>0.158188</v>
+      </c>
+      <c r="J345" s="5" t="n">
+        <v>0.631473</v>
+      </c>
+      <c r="K345" s="5" t="n">
+        <v>0.547111</v>
+      </c>
+      <c r="L345" s="5" t="n">
+        <v>1.020259</v>
+      </c>
+      <c r="M345" s="5" t="n">
+        <v>0.529484</v>
       </c>
       <c r="N345" t="inlineStr">
         <is>
@@ -38258,21 +38362,19 @@
         </is>
       </c>
       <c r="O345" s="5" t="n">
-        <v>-3.872862</v>
+        <v>4.045733</v>
       </c>
       <c r="P345" s="5" t="n">
-        <v>-1.223155</v>
+        <v>2.662846</v>
       </c>
       <c r="Q345" s="5" t="n">
-        <v>-4.20835</v>
+        <v>2.605052</v>
       </c>
       <c r="R345" s="5" t="n">
-        <v>-1.860531</v>
-      </c>
-      <c r="S345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.155346</v>
+      </c>
+      <c r="S345" s="5" t="n">
+        <v>5.48201</v>
       </c>
     </row>
     <row r="346">
@@ -38283,17 +38385,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -38301,65 +38403,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F346" s="5" t="n">
+        <v>-0.00266</v>
+      </c>
+      <c r="G346" s="5" t="n">
+        <v>-0.003197</v>
+      </c>
+      <c r="H346" s="5" t="n">
+        <v>-0.000728</v>
+      </c>
+      <c r="I346" s="5" t="n">
+        <v>-0.000264</v>
       </c>
       <c r="J346" s="5" t="n">
-        <v>0.011647</v>
+        <v>-0.005979</v>
       </c>
       <c r="K346" s="5" t="n">
-        <v>0.006311</v>
+        <v>-0.020268</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>0.046182</v>
-      </c>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.011953</v>
+      </c>
+      <c r="M346" s="5" t="n">
+        <v>-0.012522</v>
       </c>
       <c r="N346" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O346" s="5" t="n">
+        <v>-0.025008</v>
       </c>
       <c r="P346" s="5" t="n">
-        <v>0.08412</v>
+        <v>-0.037709</v>
       </c>
       <c r="Q346" s="5" t="n">
-        <v>0.182703</v>
-      </c>
-      <c r="R346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.181281</v>
+      </c>
+      <c r="R346" s="5" t="n">
+        <v>-0.09063400000000001</v>
+      </c>
+      <c r="S346" s="5" t="n">
+        <v>-0.14842</v>
       </c>
     </row>
     <row r="347">
@@ -38375,12 +38461,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Loss for the period $</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -38438,21 +38524,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P347" s="5" t="n">
-        <v>-2.625137</v>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q347" s="5" t="n">
-        <v>-2.423771</v>
-      </c>
-      <c r="R347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.423771</v>
+      </c>
+      <c r="R347" s="5" t="n">
+        <v>4.064712</v>
+      </c>
+      <c r="S347" s="5" t="n">
+        <v>5.33359</v>
       </c>
     </row>
     <row r="348">
@@ -38468,12 +38552,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the period</t>
+          <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -38531,21 +38615,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P348" s="5" t="n">
-        <v>-1.223155</v>
-      </c>
-      <c r="Q348" s="5" t="n">
-        <v>-3.340103</v>
-      </c>
-      <c r="R348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R348" s="5" t="n">
+        <v>1.207633</v>
+      </c>
+      <c r="S348" s="5" t="n">
+        <v>-3.560663</v>
       </c>
     </row>
     <row r="349">
@@ -38556,71 +38640,83 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Accounting and audit fees $</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
-      <c r="E349" s="5" t="n">
-        <v>0.047839</v>
-      </c>
-      <c r="F349" s="5" t="n">
-        <v>0.029285</v>
-      </c>
-      <c r="G349" s="5" t="n">
-        <v>0.024687</v>
-      </c>
-      <c r="H349" s="5" t="n">
-        <v>0.020554</v>
-      </c>
-      <c r="I349" s="5" t="n">
-        <v>0.029798</v>
-      </c>
-      <c r="J349" s="5" t="n">
-        <v>0.03344</v>
-      </c>
-      <c r="K349" s="5" t="n">
-        <v>0.032086</v>
-      </c>
-      <c r="L349" s="5" t="n">
-        <v>0.031792</v>
-      </c>
-      <c r="M349" s="5" t="n">
-        <v>0.033384</v>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N349" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O349" s="5" t="n">
+        <v>-4.020725</v>
+      </c>
+      <c r="P349" s="5" t="n">
+        <v>-2.625137</v>
+      </c>
+      <c r="Q349" s="5" t="n">
+        <v>-3.365909</v>
+      </c>
+      <c r="R349" s="5" t="n">
+        <v>-5.272345</v>
+      </c>
+      <c r="S349" s="5" t="n">
+        <v>-1.772927</v>
       </c>
     </row>
     <row r="350">
@@ -38631,19 +38727,15 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Foreign currency translation</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -38669,47 +38761,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J350" s="5" t="n">
-        <v>0.063052</v>
-      </c>
-      <c r="K350" s="5" t="n">
-        <v>0.039157</v>
-      </c>
-      <c r="L350" s="5" t="n">
-        <v>0.016272</v>
-      </c>
-      <c r="M350" s="5" t="n">
-        <v>0.015069</v>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N350" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O350" s="5" t="n">
+        <v>-0.147863</v>
+      </c>
+      <c r="P350" s="5" t="n">
+        <v>-1.401982</v>
+      </c>
+      <c r="Q350" s="5" t="n">
+        <v>0.842441</v>
+      </c>
+      <c r="R350" s="5" t="n">
+        <v>-3.411814</v>
+      </c>
+      <c r="S350" s="5" t="n">
+        <v>2.580225</v>
       </c>
     </row>
     <row r="351">
@@ -38720,12 +38810,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Shareholder relations, marketing, and conferences</t>
+          <t>Comprehensive loss (income) for the year</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -38744,23 +38834,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H351" s="5" t="n">
-        <v>0.000995</v>
-      </c>
-      <c r="I351" s="5" t="n">
-        <v>0.003474</v>
-      </c>
-      <c r="J351" s="5" t="n">
-        <v>0.056314</v>
-      </c>
-      <c r="K351" s="5" t="n">
-        <v>0.021284</v>
-      </c>
-      <c r="L351" s="5" t="n">
-        <v>0.056634</v>
-      </c>
-      <c r="M351" s="5" t="n">
-        <v>0.028566</v>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N351" t="inlineStr">
         <is>
@@ -38782,15 +38884,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R351" s="5" t="n">
+        <v>1.860531</v>
+      </c>
+      <c r="S351" s="5" t="n">
+        <v>4.353152</v>
       </c>
     </row>
     <row r="352">
@@ -38801,77 +38899,77 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr"/>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="F352" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="G352" s="5" t="n">
-        <v>0.050547</v>
+        <v>1e-08</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I352" s="5" t="n">
-        <v>0.071078</v>
-      </c>
-      <c r="J352" s="5" t="n">
-        <v>0.172108</v>
-      </c>
-      <c r="K352" s="5" t="n">
-        <v>0.326443</v>
-      </c>
-      <c r="L352" s="5" t="n">
-        <v>0.670354</v>
-      </c>
-      <c r="M352" s="5" t="n">
-        <v>0.178785</v>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N352" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O352" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="P352" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="Q352" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="R352" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="S352" s="5" t="n">
+        <v>1e-08</v>
       </c>
     </row>
     <row r="353">
@@ -38882,19 +38980,15 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -38910,53 +39004,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H353" s="5" t="n">
-        <v>-0.612548</v>
-      </c>
-      <c r="I353" s="5" t="n">
-        <v>-0.157923</v>
-      </c>
-      <c r="J353" s="5" t="n">
-        <v>-0.625494</v>
-      </c>
-      <c r="K353" s="5" t="n">
-        <v>-0.526843</v>
-      </c>
-      <c r="L353" s="5" t="n">
-        <v>-1.008307</v>
-      </c>
-      <c r="M353" s="5" t="n">
-        <v>-0.516962</v>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O353" s="5" t="n">
+        <v>107.819163</v>
+      </c>
+      <c r="P353" s="5" t="n">
+        <v>129.079858</v>
+      </c>
+      <c r="Q353" s="5" t="n">
+        <v>155.412367</v>
+      </c>
+      <c r="R353" s="5" t="n">
+        <v>187.635124</v>
+      </c>
+      <c r="S353" s="5" t="n">
+        <v>248.845949</v>
       </c>
     </row>
     <row r="354">
@@ -38965,14 +39061,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>OTHER COMPREHENSIVE LOSS (INCOME)</t>
-        </is>
-      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Foreign currency translation</t>
+          <t>December 31, 2024 December</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -39001,17 +39093,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J354" s="5" t="n">
-        <v>-3.379606</v>
-      </c>
-      <c r="K354" s="5" t="n">
-        <v>0.352609</v>
-      </c>
-      <c r="L354" s="5" t="n">
-        <v>0.740061</v>
-      </c>
-      <c r="M354" s="5" t="n">
-        <v>-0.920526</v>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
@@ -39028,15 +39128,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q354" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="R354" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="S354" t="inlineStr">
         <is>
@@ -39052,15 +39148,19 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS (INCOME)</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Comprehensive loss (income) for the year $</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>Deferred income tax expense</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -39086,17 +39186,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J355" s="5" t="n">
-        <v>-2.754112</v>
-      </c>
-      <c r="K355" s="5" t="n">
-        <v>0.879452</v>
-      </c>
-      <c r="L355" s="5" t="n">
-        <v>1.748367</v>
-      </c>
-      <c r="M355" s="5" t="n">
-        <v>-0.403564</v>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
@@ -39113,15 +39221,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q355" s="5" t="n">
+        <v>0.942138</v>
+      </c>
+      <c r="R355" s="5" t="n">
+        <v>1.207633</v>
       </c>
       <c r="S355" t="inlineStr">
         <is>
@@ -39137,17 +39241,17 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS (INCOME)</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>Comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -39175,42 +39279,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J356" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="K356" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="L356" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="M356" s="5" t="n">
-        <v>1e-08</v>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O356" s="5" t="n">
+        <v>-3.872862</v>
+      </c>
+      <c r="P356" s="5" t="n">
+        <v>-1.223155</v>
+      </c>
+      <c r="Q356" s="5" t="n">
+        <v>-4.20835</v>
+      </c>
+      <c r="R356" s="5" t="n">
+        <v>-1.860531</v>
       </c>
       <c r="S356" t="inlineStr">
         <is>
@@ -39226,43 +39330,57 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Basic and fully diluted</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F357" s="5" t="n">
-        <v>18.287123</v>
-      </c>
-      <c r="G357" s="5" t="n">
-        <v>22.62411</v>
-      </c>
-      <c r="H357" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="I357" s="5" t="n">
-        <v>9.384931</v>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J357" s="5" t="n">
-        <v>54.907378</v>
+        <v>0.011647</v>
       </c>
       <c r="K357" s="5" t="n">
-        <v>54.916547</v>
+        <v>0.006311</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>60.284492</v>
-      </c>
-      <c r="M357" s="5" t="n">
-        <v>62.566547</v>
+        <v>0.046182</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
@@ -39274,15 +39392,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P357" s="5" t="n">
+        <v>0.08412</v>
+      </c>
+      <c r="Q357" s="5" t="n">
+        <v>0.182703</v>
       </c>
       <c r="R357" t="inlineStr">
         <is>
@@ -39303,15 +39417,19 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Foreign currency translation</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr"/>
+          <t>Loss for the period $</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -39342,11 +39460,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K358" s="5" t="n">
-        <v>0.352609</v>
-      </c>
-      <c r="L358" s="5" t="n">
-        <v>0.740061</v>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
@@ -39363,15 +39485,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P358" s="5" t="n">
+        <v>-2.625137</v>
+      </c>
+      <c r="Q358" s="5" t="n">
+        <v>-2.423771</v>
       </c>
       <c r="R358" t="inlineStr">
         <is>
@@ -39392,12 +39510,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
+          <t>Comprehensive loss for the period</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -39435,11 +39553,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K359" s="5" t="n">
-        <v>-0.879452</v>
-      </c>
-      <c r="L359" s="5" t="n">
-        <v>-1.748367</v>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M359" t="inlineStr">
         <is>
@@ -39456,15 +39578,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P359" s="5" t="n">
+        <v>-1.223155</v>
+      </c>
+      <c r="Q359" s="5" t="n">
+        <v>-3.340103</v>
       </c>
       <c r="R359" t="inlineStr">
         <is>
@@ -39485,59 +39603,41 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE LOSS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounting and audit fees $</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" s="5" t="n">
+        <v>0.047839</v>
+      </c>
+      <c r="F360" s="5" t="n">
+        <v>0.029285</v>
+      </c>
+      <c r="G360" s="5" t="n">
+        <v>0.024687</v>
+      </c>
+      <c r="H360" s="5" t="n">
+        <v>0.020554</v>
+      </c>
+      <c r="I360" s="5" t="n">
+        <v>0.029798</v>
+      </c>
+      <c r="J360" s="5" t="n">
+        <v>0.03344</v>
       </c>
       <c r="K360" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.032086</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.031792</v>
+      </c>
+      <c r="M360" s="5" t="n">
+        <v>0.033384</v>
       </c>
       <c r="N360" t="inlineStr">
         <is>
@@ -39583,10 +39683,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 8(b))</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -39613,20 +39717,16 @@
         </is>
       </c>
       <c r="J361" s="5" t="n">
-        <v>0.172108</v>
+        <v>0.063052</v>
       </c>
       <c r="K361" s="5" t="n">
-        <v>0.326443</v>
-      </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.039157</v>
+      </c>
+      <c r="L361" s="5" t="n">
+        <v>0.016272</v>
+      </c>
+      <c r="M361" s="5" t="n">
+        <v>0.015069</v>
       </c>
       <c r="N361" t="inlineStr">
         <is>
@@ -39667,12 +39767,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Foreign currency translation</t>
+          <t>Shareholder relations, marketing, and conferences</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -39691,31 +39791,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H362" s="5" t="n">
+        <v>0.000995</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>-0.195262</v>
+        <v>0.003474</v>
       </c>
       <c r="J362" s="5" t="n">
-        <v>-3.379606</v>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.056314</v>
+      </c>
+      <c r="K362" s="5" t="n">
+        <v>0.021284</v>
+      </c>
+      <c r="L362" s="5" t="n">
+        <v>0.056634</v>
+      </c>
+      <c r="M362" s="5" t="n">
+        <v>0.028566</v>
       </c>
       <c r="N362" t="inlineStr">
         <is>
@@ -39756,12 +39848,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Comprehensive income for the year $</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -39775,10 +39867,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G363" s="5" t="n">
+        <v>0.050547</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
@@ -39786,25 +39876,19 @@
         </is>
       </c>
       <c r="I363" s="5" t="n">
-        <v>-0.037339</v>
+        <v>0.071078</v>
       </c>
       <c r="J363" s="5" t="n">
-        <v>-2.754112</v>
-      </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.172108</v>
+      </c>
+      <c r="K363" s="5" t="n">
+        <v>0.326443</v>
+      </c>
+      <c r="L363" s="5" t="n">
+        <v>0.670354</v>
+      </c>
+      <c r="M363" s="5" t="n">
+        <v>0.178785</v>
       </c>
       <c r="N363" t="inlineStr">
         <is>
@@ -39845,17 +39929,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -39874,28 +39958,22 @@
         </is>
       </c>
       <c r="H364" s="5" t="n">
-        <v>1.1e-07</v>
+        <v>-0.612548</v>
       </c>
       <c r="I364" s="5" t="n">
-        <v>2e-08</v>
+        <v>-0.157923</v>
       </c>
       <c r="J364" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.625494</v>
+      </c>
+      <c r="K364" s="5" t="n">
+        <v>-0.526843</v>
+      </c>
+      <c r="L364" s="5" t="n">
+        <v>-1.008307</v>
+      </c>
+      <c r="M364" s="5" t="n">
+        <v>-0.516962</v>
       </c>
       <c r="N364" t="inlineStr">
         <is>
@@ -39936,26 +40014,24 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER COMPREHENSIVE LOSS (INCOME)</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Foreign currency translation</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F365" s="5" t="n">
-        <v>0.000437</v>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -39967,28 +40043,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I365" s="5" t="n">
-        <v>-0.02838</v>
-      </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J365" s="5" t="n">
+        <v>-3.379606</v>
+      </c>
+      <c r="K365" s="5" t="n">
+        <v>0.352609</v>
+      </c>
+      <c r="L365" s="5" t="n">
+        <v>0.740061</v>
+      </c>
+      <c r="M365" s="5" t="n">
+        <v>-0.920526</v>
       </c>
       <c r="N365" t="inlineStr">
         <is>
@@ -40029,12 +40099,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER COMPREHENSIVE LOSS (INCOME)</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets (Note 5(b))</t>
+          <t>Comprehensive loss (income) for the year $</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -40053,33 +40123,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H366" s="5" t="n">
-        <v>0.486197</v>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J366" s="5" t="n">
+        <v>-2.754112</v>
+      </c>
+      <c r="K366" s="5" t="n">
+        <v>0.879452</v>
+      </c>
+      <c r="L366" s="5" t="n">
+        <v>1.748367</v>
+      </c>
+      <c r="M366" s="5" t="n">
+        <v>-0.403564</v>
       </c>
       <c r="N366" t="inlineStr">
         <is>
@@ -40120,15 +40184,19 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME</t>
+          <t>OTHER COMPREHENSIVE LOSS (INCOME)</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Foreign currency translation (Note 11)</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr"/>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -40149,28 +40217,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I367" s="5" t="n">
-        <v>-0.195262</v>
-      </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J367" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="K367" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="L367" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="M367" s="5" t="n">
+        <v>1e-08</v>
       </c>
       <c r="N367" t="inlineStr">
         <is>
@@ -40211,12 +40273,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Comprehensive loss (income) for the year $</t>
+          <t>Basic and fully diluted</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -40225,41 +40287,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F368" s="5" t="n">
+        <v>18.287123</v>
+      </c>
+      <c r="G368" s="5" t="n">
+        <v>22.62411</v>
       </c>
       <c r="H368" s="5" t="n">
-        <v>0.612548</v>
+        <v>23</v>
       </c>
       <c r="I368" s="5" t="n">
-        <v>-0.037339</v>
-      </c>
-      <c r="J368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.384931</v>
+      </c>
+      <c r="J368" s="5" t="n">
+        <v>54.907378</v>
+      </c>
+      <c r="K368" s="5" t="n">
+        <v>54.916547</v>
+      </c>
+      <c r="L368" s="5" t="n">
+        <v>60.284492</v>
+      </c>
+      <c r="M368" s="5" t="n">
+        <v>62.566547</v>
       </c>
       <c r="N368" t="inlineStr">
         <is>
@@ -40300,12 +40350,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>OTHER COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Basic and fully diluted(1)</t>
+          <t>Foreign currency translation</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -40324,26 +40374,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H369" s="5" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="I369" s="5" t="n">
-        <v>9.384931</v>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K369" s="5" t="n">
+        <v>0.352609</v>
+      </c>
+      <c r="L369" s="5" t="n">
+        <v>0.740061</v>
       </c>
       <c r="M369" t="inlineStr">
         <is>
@@ -40389,15 +40439,19 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Consultants (Note 6)</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -40408,11 +40462,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G370" s="5" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="H370" s="5" t="n">
-        <v>0.028</v>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -40424,15 +40482,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K370" s="5" t="n">
+        <v>-0.879452</v>
+      </c>
+      <c r="L370" s="5" t="n">
+        <v>-1.748367</v>
       </c>
       <c r="M370" t="inlineStr">
         <is>
@@ -40478,17 +40532,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Management fees (Note 6)</t>
+          <t>Loss per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -40501,11 +40555,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G371" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H371" s="5" t="n">
-        <v>0.05</v>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -40517,15 +40575,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K371" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="L371" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="M371" t="inlineStr">
         <is>
@@ -40576,36 +40630,40 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Shareholder relations</t>
+          <t>Share-based compensation (Note 8(b))</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" s="5" t="n">
-        <v>0.000147</v>
-      </c>
-      <c r="F372" s="5" t="n">
-        <v>0.001537</v>
-      </c>
-      <c r="G372" s="5" t="n">
-        <v>0.001221</v>
-      </c>
-      <c r="H372" s="5" t="n">
-        <v>0.000995</v>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J372" s="5" t="n">
+        <v>0.172108</v>
+      </c>
+      <c r="K372" s="5" t="n">
+        <v>0.326443</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -40656,12 +40714,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets (Note 4)</t>
+          <t>Foreign currency translation</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -40680,18 +40738,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H373" s="5" t="n">
-        <v>0.486197</v>
-      </c>
-      <c r="I373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I373" s="5" t="n">
+        <v>-0.195262</v>
+      </c>
+      <c r="J373" s="5" t="n">
+        <v>-3.379606</v>
       </c>
       <c r="K373" t="inlineStr">
         <is>
@@ -40747,40 +40803,40 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E374" s="5" t="n">
-        <v>-0.054942</v>
-      </c>
-      <c r="F374" s="5" t="n">
-        <v>-0.451043</v>
-      </c>
-      <c r="G374" s="5" t="n">
-        <v>-0.271749</v>
-      </c>
-      <c r="H374" s="5" t="n">
-        <v>-0.612548</v>
-      </c>
-      <c r="I374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Comprehensive income for the year $</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I374" s="5" t="n">
+        <v>-0.037339</v>
+      </c>
+      <c r="J374" s="5" t="n">
+        <v>-2.754112</v>
       </c>
       <c r="K374" t="inlineStr">
         <is>
@@ -40836,12 +40892,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Loss per share basic and diluted $</t>
+          <t>Loss per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -40859,21 +40915,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G375" s="5" t="n">
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H375" s="5" t="n">
+        <v>1.1e-07</v>
+      </c>
+      <c r="I375" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="J375" s="5" t="n">
         <v>1e-08</v>
-      </c>
-      <c r="H375" s="5" t="n">
-        <v>3e-08</v>
-      </c>
-      <c r="I375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
@@ -40934,30 +40988,34 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Consultants (Note 5)</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr"/>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F376" s="5" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G376" s="5" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.000437</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I376" s="5" t="n">
+        <v>-0.02838</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
@@ -41023,7 +41081,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Due diligence costs</t>
+          <t>Write-off of exploration and evaluation assets (Note 5(b))</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -41032,18 +41090,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F377" s="5" t="n">
-        <v>0.006587</v>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H377" s="5" t="n">
+        <v>0.486197</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
@@ -41109,39 +41167,37 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Management fees (Note 5)</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Foreign currency translation (Note 11)</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F378" s="5" t="n">
-        <v>0.042375</v>
-      </c>
-      <c r="G378" s="5" t="n">
-        <v>0.09</v>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I378" s="5" t="n">
+        <v>-0.195262</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -41202,12 +41258,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 4(c))</t>
+          <t>Comprehensive loss (income) for the year $</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -41216,21 +41272,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F379" s="5" t="n">
-        <v>0.164015</v>
-      </c>
-      <c r="G379" s="5" t="n">
-        <v>0.050547</v>
-      </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H379" s="5" t="n">
+        <v>0.612548</v>
+      </c>
+      <c r="I379" s="5" t="n">
+        <v>-0.037339</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
@@ -41291,12 +41347,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Consultants (Note 9)</t>
+          <t>Basic and fully diluted(1)</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -41305,23 +41361,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F380" s="5" t="n">
-        <v>0.028</v>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H380" s="5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I380" s="5" t="n">
+        <v>9.384931</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
@@ -41387,31 +41441,25 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Management fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Consultants (Note 6)</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F381" s="5" t="n">
-        <v>0.042375</v>
-      </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G381" s="5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="H381" s="5" t="n">
+        <v>0.028</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
@@ -41482,27 +41530,29 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 6(c))</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>Management fees (Note 6)</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F382" s="5" t="n">
-        <v>0.164015</v>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G382" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H382" s="5" t="n">
+        <v>0.05</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
@@ -41573,29 +41623,21 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Transfer agent and regulatory fees (Note 5)</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Shareholder relations</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" s="5" t="n">
-        <v>0.006</v>
+        <v>0.000147</v>
       </c>
       <c r="F383" s="5" t="n">
-        <v>0.085439</v>
-      </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001537</v>
+      </c>
+      <c r="G383" s="5" t="n">
+        <v>0.001221</v>
+      </c>
+      <c r="H383" s="5" t="n">
+        <v>0.000995</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
@@ -41661,36 +41703,32 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Interest income $</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Write-off of exploration and evaluation assets (Note 4)</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F384" s="5" t="n">
-        <v>0.00266</v>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H384" s="5" t="n">
+        <v>0.486197</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
@@ -41756,34 +41794,30 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>OTHER INCOME</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E385" s="5" t="n">
-        <v>8.301149000000001</v>
+        <v>-0.054942</v>
       </c>
       <c r="F385" s="5" t="n">
-        <v>18.287123</v>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.451043</v>
+      </c>
+      <c r="G385" s="5" t="n">
+        <v>-0.271749</v>
+      </c>
+      <c r="H385" s="5" t="n">
+        <v>-0.612548</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
@@ -41849,82 +41883,1837 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
+          <t>OTHER INCOME</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Loss per share basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G386" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H386" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Consultants (Note 5)</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F387" s="5" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G387" s="5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Due diligence costs</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F388" s="5" t="n">
+        <v>0.006587</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Management fees (Note 5)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F389" s="5" t="n">
+        <v>0.042375</v>
+      </c>
+      <c r="G389" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 4(c))</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F390" s="5" t="n">
+        <v>0.164015</v>
+      </c>
+      <c r="G390" s="5" t="n">
+        <v>0.050547</v>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Consultants (Note 9)</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F391" s="5" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Management fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F392" s="5" t="n">
+        <v>0.042375</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 6(c))</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F393" s="5" t="n">
+        <v>0.164015</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Transfer agent and regulatory fees (Note 5)</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E394" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F394" s="5" t="n">
+        <v>0.085439</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>OTHER INCOME</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Interest income $</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F395" s="5" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
           <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr">
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E396" s="5" t="n">
+        <v>8.301149000000001</v>
+      </c>
+      <c r="F396" s="5" t="n">
+        <v>18.287123</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
         <is>
           <t>Fully diluted</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
-      <c r="E386" s="5" t="n">
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" s="5" t="n">
         <v>8.301149000000001</v>
       </c>
-      <c r="F386" s="5" t="n">
+      <c r="F397" s="5" t="n">
         <v>28.147123</v>
       </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S386" t="inlineStr">
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Incorporation to</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Office costs</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" s="5" t="n">
+        <v>0.000956</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Trust and regulatory fees</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E400" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E401" s="5" t="n">
+        <v>-0.054942</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Deficit – Beginning of period $</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Deficit – End of period $</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" s="5" t="n">
+        <v>0.054942</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E404" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Basic and fully diluted</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" s="5" t="n">
+        <v>6.356772</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
         <is>
           <t>-</t>
         </is>
